--- a/2026-09-28_Audited_Fiber_Models_Rev2/03_FWA_Business_Case_Combined_Rev2.xlsx
+++ b/2026-09-28_Audited_Fiber_Models_Rev2/03_FWA_Business_Case_Combined_Rev2.xlsx
@@ -575,7 +575,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -815,7 +814,7 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>2453270</v>
+        <v>2452688</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -840,7 +839,7 @@
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>6139</v>
+        <v>6138</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -865,7 +864,7 @@
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -874,7 +873,7 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Audited short node connections &lt;=1 km (28.2%)</t>
+          <t>Audited short node connections &lt;=1 km (30.3%)</t>
         </is>
       </c>
     </row>
@@ -915,7 +914,7 @@
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>297</v>
+        <v>275</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
@@ -924,7 +923,7 @@
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Audited asset within 3 km (29.7%)</t>
+          <t>Audited asset within 3 km (27.5%)</t>
         </is>
       </c>
     </row>
@@ -940,7 +939,7 @@
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
@@ -949,7 +948,7 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Remote candidate sites &gt;3 km (25.1%)</t>
+          <t>Remote candidate sites &gt;3 km (25.2%)</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1370,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1454,35 +1452,45 @@
         <f>SUM(D5:M5)</f>
         <v/>
       </c>
-      <c r="D5" s="15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E5" s="15" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F5" s="15" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G5" s="15" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H5" s="15" t="n">
-        <v>5000</v>
-      </c>
-      <c r="I5" s="15" t="n">
-        <v>5000</v>
-      </c>
-      <c r="J5" s="15" t="n">
-        <v>5000</v>
-      </c>
-      <c r="K5" s="15" t="n">
-        <v>5000</v>
-      </c>
-      <c r="L5" s="15" t="n">
-        <v>5000</v>
-      </c>
-      <c r="M5" s="15" t="n">
-        <v>5000</v>
+      <c r="D5" s="15">
+        <f>'Assumptions &amp; Levers'!</f>
+        <v/>
+      </c>
+      <c r="E5" s="15">
+        <f>D5+'Assumptions &amp; Levers'!</f>
+        <v/>
+      </c>
+      <c r="F5" s="15">
+        <f>E5+'Assumptions &amp; Levers'!</f>
+        <v/>
+      </c>
+      <c r="G5" s="15">
+        <f>F5+'Assumptions &amp; Levers'!</f>
+        <v/>
+      </c>
+      <c r="H5" s="15">
+        <f>G5+'Assumptions &amp; Levers'!</f>
+        <v/>
+      </c>
+      <c r="I5" s="15">
+        <f>H5</f>
+        <v/>
+      </c>
+      <c r="J5" s="15">
+        <f>I5</f>
+        <v/>
+      </c>
+      <c r="K5" s="15">
+        <f>J5</f>
+        <v/>
+      </c>
+      <c r="L5" s="15">
+        <f>K5</f>
+        <v/>
+      </c>
+      <c r="M5" s="15">
+        <f>L5</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -1639,34 +1647,34 @@
         <v/>
       </c>
       <c r="D9" s="17" t="n">
-        <v>6.61</v>
+        <v>7</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>13.21</v>
+        <v>14</v>
       </c>
       <c r="F9" s="17" t="n">
-        <v>19.82</v>
+        <v>21</v>
       </c>
       <c r="G9" s="17" t="n">
-        <v>26.43</v>
+        <v>28</v>
       </c>
       <c r="H9" s="17" t="n">
-        <v>33.03</v>
+        <v>35</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>33.03</v>
+        <v>35</v>
       </c>
       <c r="J9" s="17" t="n">
-        <v>33.03</v>
+        <v>35</v>
       </c>
       <c r="K9" s="17" t="n">
-        <v>33.03</v>
+        <v>35</v>
       </c>
       <c r="L9" s="17" t="n">
-        <v>33.03</v>
+        <v>35</v>
       </c>
       <c r="M9" s="17" t="n">
-        <v>33.03</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -1731,43 +1739,43 @@
         <v/>
       </c>
       <c r="D11" s="17">
-        <f>SUM(D7:D9)</f>
+        <f>SUM(D8:D10)</f>
         <v/>
       </c>
       <c r="E11" s="17">
-        <f>SUM(E7:E9)</f>
+        <f>SUM(E8:E10)</f>
         <v/>
       </c>
       <c r="F11" s="17">
-        <f>SUM(F7:F9)</f>
+        <f>SUM(F8:F10)</f>
         <v/>
       </c>
       <c r="G11" s="17">
-        <f>SUM(G7:G9)</f>
+        <f>SUM(G8:G10)</f>
         <v/>
       </c>
       <c r="H11" s="17">
-        <f>SUM(H7:H9)</f>
+        <f>SUM(H8:H10)</f>
         <v/>
       </c>
       <c r="I11" s="17">
-        <f>SUM(I7:I9)</f>
+        <f>SUM(I8:I10)</f>
         <v/>
       </c>
       <c r="J11" s="17">
-        <f>SUM(J7:J9)</f>
+        <f>SUM(J8:J10)</f>
         <v/>
       </c>
       <c r="K11" s="17">
-        <f>SUM(K7:K9)</f>
+        <f>SUM(K8:K10)</f>
         <v/>
       </c>
       <c r="L11" s="17">
-        <f>SUM(L7:L9)</f>
+        <f>SUM(L8:L10)</f>
         <v/>
       </c>
       <c r="M11" s="17">
-        <f>SUM(M7:M9)</f>
+        <f>SUM(M8:M10)</f>
         <v/>
       </c>
     </row>
@@ -1787,43 +1795,43 @@
         <v/>
       </c>
       <c r="D12" s="18">
-        <f>D6-D10</f>
+        <f>D7-D11</f>
         <v/>
       </c>
       <c r="E12" s="18">
-        <f>E6-E10</f>
+        <f>E7-E11</f>
         <v/>
       </c>
       <c r="F12" s="18">
-        <f>F6-F10</f>
+        <f>F7-F11</f>
         <v/>
       </c>
       <c r="G12" s="18">
-        <f>G6-G10</f>
+        <f>G7-G11</f>
         <v/>
       </c>
       <c r="H12" s="18">
-        <f>H6-H10</f>
+        <f>H7-H11</f>
         <v/>
       </c>
       <c r="I12" s="18">
-        <f>I6-I10</f>
+        <f>I7-I11</f>
         <v/>
       </c>
       <c r="J12" s="18">
-        <f>J6-J10</f>
+        <f>J7-J11</f>
         <v/>
       </c>
       <c r="K12" s="18">
-        <f>K6-K10</f>
+        <f>K7-K11</f>
         <v/>
       </c>
       <c r="L12" s="18">
-        <f>L6-L10</f>
+        <f>L7-L11</f>
         <v/>
       </c>
       <c r="M12" s="18">
-        <f>M6-M10</f>
+        <f>M7-M11</f>
         <v/>
       </c>
     </row>
@@ -1889,19 +1897,19 @@
         <v/>
       </c>
       <c r="D14" s="17" t="n">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="F14" s="17" t="n">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="H14" s="17" t="n">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="I14" s="17" t="n">
         <v>0</v>
@@ -1981,43 +1989,43 @@
         <v/>
       </c>
       <c r="D16" s="17">
-        <f>SUM(D12:D14)</f>
+        <f>SUM(D13:D15)</f>
         <v/>
       </c>
       <c r="E16" s="17">
-        <f>SUM(E12:E14)</f>
+        <f>SUM(E13:E15)</f>
         <v/>
       </c>
       <c r="F16" s="17">
-        <f>SUM(F12:F14)</f>
+        <f>SUM(F13:F15)</f>
         <v/>
       </c>
       <c r="G16" s="17">
-        <f>SUM(G12:G14)</f>
+        <f>SUM(G13:G15)</f>
         <v/>
       </c>
       <c r="H16" s="17">
-        <f>SUM(H12:H14)</f>
+        <f>SUM(H13:H15)</f>
         <v/>
       </c>
       <c r="I16" s="17">
-        <f>SUM(I12:I14)</f>
+        <f>SUM(I13:I15)</f>
         <v/>
       </c>
       <c r="J16" s="17">
-        <f>SUM(J12:J14)</f>
+        <f>SUM(J13:J15)</f>
         <v/>
       </c>
       <c r="K16" s="17">
-        <f>SUM(K12:K14)</f>
+        <f>SUM(K13:K15)</f>
         <v/>
       </c>
       <c r="L16" s="17">
-        <f>SUM(L12:L14)</f>
+        <f>SUM(L13:L15)</f>
         <v/>
       </c>
       <c r="M16" s="17">
-        <f>SUM(M12:M14)</f>
+        <f>SUM(M13:M15)</f>
         <v/>
       </c>
     </row>
@@ -2037,48 +2045,46 @@
         <v/>
       </c>
       <c r="D17" s="22">
-        <f>D11-D15</f>
+        <f>D12-D16</f>
         <v/>
       </c>
       <c r="E17" s="22">
-        <f>E11-E15</f>
+        <f>E12-E16</f>
         <v/>
       </c>
       <c r="F17" s="22">
-        <f>F11-F15</f>
+        <f>F12-F16</f>
         <v/>
       </c>
       <c r="G17" s="22">
-        <f>G11-G15</f>
+        <f>G12-G16</f>
         <v/>
       </c>
       <c r="H17" s="22">
-        <f>H11-H15</f>
+        <f>H12-H16</f>
         <v/>
       </c>
       <c r="I17" s="22">
-        <f>I11-I15</f>
+        <f>I12-I16</f>
         <v/>
       </c>
       <c r="J17" s="22">
-        <f>J11-J15</f>
+        <f>J12-J16</f>
         <v/>
       </c>
       <c r="K17" s="22">
-        <f>K11-K15</f>
+        <f>K12-K16</f>
         <v/>
       </c>
       <c r="L17" s="22">
-        <f>L11-L15</f>
+        <f>L12-L16</f>
         <v/>
       </c>
       <c r="M17" s="22">
-        <f>M11-M15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19"/>
+        <f>M12-M16</f>
+        <v/>
+      </c>
+    </row>
     <row r="20">
       <c r="A20" s="23" t="inlineStr">
         <is>
@@ -2126,7 +2132,7 @@
       </c>
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>4.8 Years</t>
+          <t>8.3 Years</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">

--- a/2026-09-28_Audited_Fiber_Models_Rev2/03_FWA_Business_Case_Combined_Rev2.xlsx
+++ b/2026-09-28_Audited_Fiber_Models_Rev2/03_FWA_Business_Case_Combined_Rev2.xlsx
@@ -575,6 +575,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -864,7 +865,7 @@
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -873,7 +874,7 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Audited short node connections &lt;=1 km (30.3%)</t>
+          <t>Audited short node connections &lt;=1 km (31.2%)</t>
         </is>
       </c>
     </row>
@@ -889,7 +890,7 @@
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
@@ -898,7 +899,7 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>Audited line taps &lt;=500m (17.0%)</t>
+          <t>Audited line taps &lt;=500m (17.7%)</t>
         </is>
       </c>
     </row>
@@ -914,7 +915,7 @@
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
@@ -923,7 +924,7 @@
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Audited asset within 3 km (27.5%)</t>
+          <t>Audited asset within 3 km (26.6%)</t>
         </is>
       </c>
     </row>
@@ -939,7 +940,7 @@
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
@@ -948,7 +949,7 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Remote candidate sites &gt;3 km (25.2%)</t>
+          <t>Remote candidate sites &gt;3 km (24.5%)</t>
         </is>
       </c>
     </row>
@@ -1342,18 +1343,18 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="88" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="3" max="3"/>
+    <col width="124" customWidth="1" min="4" max="4"/>
+    <col width="124" customWidth="1" min="5" max="5"/>
+    <col width="124" customWidth="1" min="6" max="6"/>
+    <col width="124" customWidth="1" min="7" max="7"/>
+    <col width="124" customWidth="1" min="8" max="8"/>
+    <col width="114" customWidth="1" min="9" max="9"/>
+    <col width="114" customWidth="1" min="10" max="10"/>
+    <col width="114" customWidth="1" min="11" max="11"/>
+    <col width="114" customWidth="1" min="12" max="12"/>
+    <col width="114" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1370,6 +1371,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1453,23 +1455,23 @@
         <v/>
       </c>
       <c r="D5" s="15">
-        <f>'Assumptions &amp; Levers'!</f>
+        <f>'Assumptions &amp; Levers'!$C$10</f>
         <v/>
       </c>
       <c r="E5" s="15">
-        <f>D5+'Assumptions &amp; Levers'!</f>
+        <f>D5+'Assumptions &amp; Levers'!$C$11</f>
         <v/>
       </c>
       <c r="F5" s="15">
-        <f>E5+'Assumptions &amp; Levers'!</f>
+        <f>E5+'Assumptions &amp; Levers'!$C$11</f>
         <v/>
       </c>
       <c r="G5" s="15">
-        <f>F5+'Assumptions &amp; Levers'!</f>
+        <f>F5+'Assumptions &amp; Levers'!$C$11</f>
         <v/>
       </c>
       <c r="H5" s="15">
-        <f>G5+'Assumptions &amp; Levers'!</f>
+        <f>G5+'Assumptions &amp; Levers'!$C$11</f>
         <v/>
       </c>
       <c r="I5" s="15">
@@ -1554,35 +1556,45 @@
         <f>SUM(D7:M7)</f>
         <v/>
       </c>
-      <c r="D7" s="17" t="n">
-        <v>68.63</v>
-      </c>
-      <c r="E7" s="17" t="n">
-        <v>144.88</v>
-      </c>
-      <c r="F7" s="17" t="n">
-        <v>221.14</v>
-      </c>
-      <c r="G7" s="17" t="n">
-        <v>282.14</v>
-      </c>
-      <c r="H7" s="17" t="n">
-        <v>327.89</v>
-      </c>
-      <c r="I7" s="17" t="n">
-        <v>347.72</v>
-      </c>
-      <c r="J7" s="17" t="n">
-        <v>358.4</v>
-      </c>
-      <c r="K7" s="17" t="n">
-        <v>364.5</v>
-      </c>
-      <c r="L7" s="17" t="n">
-        <v>369.07</v>
-      </c>
-      <c r="M7" s="17" t="n">
-        <v>374.15</v>
+      <c r="D7" s="17">
+        <f>ROUND(D6*('Assumptions &amp; Levers'!$C$20/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="E7" s="17">
+        <f>ROUND(E6*('Assumptions &amp; Levers'!$C$20/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="F7" s="17">
+        <f>ROUND(F6*('Assumptions &amp; Levers'!$C$20/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="G7" s="17">
+        <f>ROUND(G6*('Assumptions &amp; Levers'!$C$20/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="H7" s="17">
+        <f>ROUND(H6*('Assumptions &amp; Levers'!$C$20/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="I7" s="17">
+        <f>ROUND(I6*('Assumptions &amp; Levers'!$C$20/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="J7" s="17">
+        <f>ROUND(J6*('Assumptions &amp; Levers'!$C$20/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="K7" s="17">
+        <f>ROUND(K6*('Assumptions &amp; Levers'!$C$20/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="L7" s="17">
+        <f>ROUND(L6*('Assumptions &amp; Levers'!$C$20/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="M7" s="17">
+        <f>ROUND(M6*('Assumptions &amp; Levers'!$C$20/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -1600,35 +1612,45 @@
         <f>SUM(D8:M8)</f>
         <v/>
       </c>
-      <c r="D8" s="17" t="n">
-        <v>26.18</v>
-      </c>
-      <c r="E8" s="17" t="n">
-        <v>52.36</v>
-      </c>
-      <c r="F8" s="17" t="n">
-        <v>78.55</v>
-      </c>
-      <c r="G8" s="17" t="n">
-        <v>104.73</v>
-      </c>
-      <c r="H8" s="17" t="n">
-        <v>130.91</v>
-      </c>
-      <c r="I8" s="17" t="n">
-        <v>130.91</v>
-      </c>
-      <c r="J8" s="17" t="n">
-        <v>130.91</v>
-      </c>
-      <c r="K8" s="17" t="n">
-        <v>130.91</v>
-      </c>
-      <c r="L8" s="17" t="n">
-        <v>130.91</v>
-      </c>
-      <c r="M8" s="17" t="n">
-        <v>130.91</v>
+      <c r="D8" s="17">
+        <f>ROUND(D5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="E8" s="17">
+        <f>ROUND(E5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="F8" s="17">
+        <f>ROUND(F5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="G8" s="17">
+        <f>ROUND(G5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="H8" s="17">
+        <f>ROUND(H5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="I8" s="17">
+        <f>ROUND(I5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="J8" s="17">
+        <f>ROUND(J5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="K8" s="17">
+        <f>ROUND(K5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="L8" s="17">
+        <f>ROUND(L5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="M8" s="17">
+        <f>ROUND(M5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -1646,35 +1668,45 @@
         <f>SUM(D9:M9)</f>
         <v/>
       </c>
-      <c r="D9" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="E9" s="17" t="n">
-        <v>14</v>
-      </c>
-      <c r="F9" s="17" t="n">
-        <v>21</v>
-      </c>
-      <c r="G9" s="17" t="n">
-        <v>28</v>
-      </c>
-      <c r="H9" s="17" t="n">
-        <v>35</v>
-      </c>
-      <c r="I9" s="17" t="n">
-        <v>35</v>
-      </c>
-      <c r="J9" s="17" t="n">
-        <v>35</v>
-      </c>
-      <c r="K9" s="17" t="n">
-        <v>35</v>
-      </c>
-      <c r="L9" s="17" t="n">
-        <v>35</v>
-      </c>
-      <c r="M9" s="17" t="n">
-        <v>35</v>
+      <c r="D9" s="17">
+        <f>ROUND((D5*0.6564*46000*12+D5*0.3436*'Assumptions &amp; Levers'!$C$31*12)/('Assumptions &amp; Levers'!$C$5*1000000), 2)</f>
+        <v/>
+      </c>
+      <c r="E9" s="17">
+        <f>ROUND((E5*0.6564*46000*12+E5*0.3436*'Assumptions &amp; Levers'!$C$31*12)/('Assumptions &amp; Levers'!$C$5*1000000), 2)</f>
+        <v/>
+      </c>
+      <c r="F9" s="17">
+        <f>ROUND((F5*0.6564*46000*12+F5*0.3436*'Assumptions &amp; Levers'!$C$31*12)/('Assumptions &amp; Levers'!$C$5*1000000), 2)</f>
+        <v/>
+      </c>
+      <c r="G9" s="17">
+        <f>ROUND((G5*0.6564*46000*12+G5*0.3436*'Assumptions &amp; Levers'!$C$31*12)/('Assumptions &amp; Levers'!$C$5*1000000), 2)</f>
+        <v/>
+      </c>
+      <c r="H9" s="17">
+        <f>ROUND((H5*0.6564*46000*12+H5*0.3436*'Assumptions &amp; Levers'!$C$31*12)/('Assumptions &amp; Levers'!$C$5*1000000), 2)</f>
+        <v/>
+      </c>
+      <c r="I9" s="17">
+        <f>ROUND((I5*0.6564*46000*12+I5*0.3436*'Assumptions &amp; Levers'!$C$31*12)/('Assumptions &amp; Levers'!$C$5*1000000), 2)</f>
+        <v/>
+      </c>
+      <c r="J9" s="17">
+        <f>ROUND((J5*0.6564*46000*12+J5*0.3436*'Assumptions &amp; Levers'!$C$31*12)/('Assumptions &amp; Levers'!$C$5*1000000), 2)</f>
+        <v/>
+      </c>
+      <c r="K9" s="17">
+        <f>ROUND((K5*0.6564*46000*12+K5*0.3436*'Assumptions &amp; Levers'!$C$31*12)/('Assumptions &amp; Levers'!$C$5*1000000), 2)</f>
+        <v/>
+      </c>
+      <c r="L9" s="17">
+        <f>ROUND((L5*0.6564*46000*12+L5*0.3436*'Assumptions &amp; Levers'!$C$31*12)/('Assumptions &amp; Levers'!$C$5*1000000), 2)</f>
+        <v/>
+      </c>
+      <c r="M9" s="17">
+        <f>ROUND((M5*0.6564*46000*12+M5*0.3436*'Assumptions &amp; Levers'!$C$31*12)/('Assumptions &amp; Levers'!$C$5*1000000), 2)</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -1692,35 +1724,45 @@
         <f>SUM(D10:M10)</f>
         <v/>
       </c>
-      <c r="D10" s="17" t="n">
-        <v>26.18</v>
-      </c>
-      <c r="E10" s="17" t="n">
-        <v>52.36</v>
-      </c>
-      <c r="F10" s="17" t="n">
-        <v>78.55</v>
-      </c>
-      <c r="G10" s="17" t="n">
-        <v>104.73</v>
-      </c>
-      <c r="H10" s="17" t="n">
-        <v>130.91</v>
-      </c>
-      <c r="I10" s="17" t="n">
-        <v>130.91</v>
-      </c>
-      <c r="J10" s="17" t="n">
-        <v>130.91</v>
-      </c>
-      <c r="K10" s="17" t="n">
-        <v>130.91</v>
-      </c>
-      <c r="L10" s="17" t="n">
-        <v>130.91</v>
-      </c>
-      <c r="M10" s="17" t="n">
-        <v>130.91</v>
+      <c r="D10" s="17">
+        <f>ROUND(D5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="E10" s="17">
+        <f>ROUND(E5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="F10" s="17">
+        <f>ROUND(F5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="G10" s="17">
+        <f>ROUND(G5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="H10" s="17">
+        <f>ROUND(H5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="I10" s="17">
+        <f>ROUND(I5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="J10" s="17">
+        <f>ROUND(J5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="K10" s="17">
+        <f>ROUND(K5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="L10" s="17">
+        <f>ROUND(L5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="M10" s="17">
+        <f>ROUND(M5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1850,20 +1892,25 @@
         <f>SUM(D13:M13)</f>
         <v/>
       </c>
-      <c r="D13" s="17" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="E13" s="17" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="F13" s="17" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="G13" s="17" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="H13" s="17" t="n">
-        <v>41.9</v>
+      <c r="D13" s="17">
+        <f>ROUND('Assumptions &amp; Levers'!$C$10*('Assumptions &amp; Levers'!$C$21+'Assumptions &amp; Levers'!$C$22)/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="E13" s="17">
+        <f>ROUND('Assumptions &amp; Levers'!$C$11*('Assumptions &amp; Levers'!$C$21+'Assumptions &amp; Levers'!$C$22)/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="F13" s="17">
+        <f>ROUND('Assumptions &amp; Levers'!$C$11*('Assumptions &amp; Levers'!$C$21+'Assumptions &amp; Levers'!$C$22)/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="G13" s="17">
+        <f>ROUND('Assumptions &amp; Levers'!$C$11*('Assumptions &amp; Levers'!$C$21+'Assumptions &amp; Levers'!$C$22)/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="H13" s="17">
+        <f>ROUND('Assumptions &amp; Levers'!$C$11*('Assumptions &amp; Levers'!$C$21+'Assumptions &amp; Levers'!$C$22)/1000000, 2)</f>
+        <v/>
       </c>
       <c r="I13" s="17" t="n">
         <v>0</v>
@@ -1896,20 +1943,25 @@
         <f>SUM(D14:M14)</f>
         <v/>
       </c>
-      <c r="D14" s="17" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="E14" s="17" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="F14" s="17" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="G14" s="17" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="H14" s="17" t="n">
-        <v>2.94</v>
+      <c r="D14" s="17">
+        <f>ROUND('Assumptions &amp; Levers'!$C$11*(0.6564*'Assumptions &amp; Levers'!$C$25+0.3436*'Assumptions &amp; Levers'!$C$27)/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="E14" s="17">
+        <f>ROUND('Assumptions &amp; Levers'!$C$11*(0.6564*'Assumptions &amp; Levers'!$C$25+0.3436*'Assumptions &amp; Levers'!$C$27)/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="F14" s="17">
+        <f>ROUND('Assumptions &amp; Levers'!$C$11*(0.6564*'Assumptions &amp; Levers'!$C$25+0.3436*'Assumptions &amp; Levers'!$C$27)/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="G14" s="17">
+        <f>ROUND('Assumptions &amp; Levers'!$C$11*(0.6564*'Assumptions &amp; Levers'!$C$25+0.3436*'Assumptions &amp; Levers'!$C$27)/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="H14" s="17">
+        <f>ROUND('Assumptions &amp; Levers'!$C$11*(0.6564*'Assumptions &amp; Levers'!$C$25+0.3436*'Assumptions &amp; Levers'!$C$27)/1000000, 2)</f>
+        <v/>
       </c>
       <c r="I14" s="17" t="n">
         <v>0</v>
@@ -1942,35 +1994,45 @@
         <f>SUM(D15:M15)</f>
         <v/>
       </c>
-      <c r="D15" s="17" t="n">
-        <v>24.75</v>
-      </c>
-      <c r="E15" s="17" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="F15" s="17" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="G15" s="17" t="n">
-        <v>22</v>
-      </c>
-      <c r="H15" s="17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="I15" s="17" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="J15" s="17" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K15" s="17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="L15" s="17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="M15" s="17" t="n">
-        <v>1.83</v>
+      <c r="D15" s="17">
+        <f>ROUND(D6*'Assumptions &amp; Levers'!$C$23/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="E15" s="17">
+        <f>ROUND((E6-D6)*'Assumptions &amp; Levers'!$C$23/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="F15" s="17">
+        <f>ROUND((F6-E6)*'Assumptions &amp; Levers'!$C$23/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="G15" s="17">
+        <f>ROUND((G6-F6)*'Assumptions &amp; Levers'!$C$23/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="H15" s="17">
+        <f>ROUND((H6-G6)*'Assumptions &amp; Levers'!$C$23/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="I15" s="17">
+        <f>ROUND((I6-H6)*'Assumptions &amp; Levers'!$C$23/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="J15" s="17">
+        <f>ROUND((J6-I6)*'Assumptions &amp; Levers'!$C$23/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="K15" s="17">
+        <f>ROUND((K6-J6)*'Assumptions &amp; Levers'!$C$23/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="L15" s="17">
+        <f>ROUND((L6-K6)*'Assumptions &amp; Levers'!$C$23/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="M15" s="17">
+        <f>ROUND((M6-L6)*'Assumptions &amp; Levers'!$C$23/1000000, 2)</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -2085,6 +2147,63 @@
         <v/>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>Cumulative Free Cash Flow ($M)</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>Cash Flow</t>
+        </is>
+      </c>
+      <c r="C18" s="21">
+        <f>M18</f>
+        <v/>
+      </c>
+      <c r="D18" s="22">
+        <f>D17</f>
+        <v/>
+      </c>
+      <c r="E18" s="22">
+        <f>D18+E17</f>
+        <v/>
+      </c>
+      <c r="F18" s="22">
+        <f>E18+F17</f>
+        <v/>
+      </c>
+      <c r="G18" s="22">
+        <f>F18+G17</f>
+        <v/>
+      </c>
+      <c r="H18" s="22">
+        <f>G18+H17</f>
+        <v/>
+      </c>
+      <c r="I18" s="22">
+        <f>H18+I17</f>
+        <v/>
+      </c>
+      <c r="J18" s="22">
+        <f>I18+J17</f>
+        <v/>
+      </c>
+      <c r="K18" s="22">
+        <f>J18+K17</f>
+        <v/>
+      </c>
+      <c r="L18" s="22">
+        <f>K18+L17</f>
+        <v/>
+      </c>
+      <c r="M18" s="22">
+        <f>L18+M17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="23" t="inlineStr">
         <is>
@@ -2099,7 +2218,7 @@
         </is>
       </c>
       <c r="B21" s="24">
-        <f>NPV(0.12, D17:M17)</f>
+        <f>NPV('Assumptions &amp; Levers'!$C$6, D17:M17)</f>
         <v/>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -2148,12 +2267,12 @@
         </is>
       </c>
       <c r="B24" s="24">
-        <f>$D$16+$E$16</f>
+        <f>ABS(MIN(0, MIN(D18:M18)))</f>
         <v/>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Maximum cash trough before self-funding</t>
+          <t>Maximum cumulative cash deficit before self-funding</t>
         </is>
       </c>
     </row>

--- a/2026-09-28_Audited_Fiber_Models_Rev2/03_FWA_Business_Case_Combined_Rev2.xlsx
+++ b/2026-09-28_Audited_Fiber_Models_Rev2/03_FWA_Business_Case_Combined_Rev2.xlsx
@@ -551,20 +551,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="101" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="47" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="84" customWidth="1" min="5" max="5"/>
+    <col width="88" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>FWA 5G n50 (100 MHz) — Combined Hybrid Dual Optimization Financial Model (Revision 2 Audited)</t>
+          <t>FWA 5G n50 (60 MHz) — Combined Hybrid Dual Optimization Financial Model (Revision 2 Audited)</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>26000</v>
+        <v>75000</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
@@ -1286,20 +1286,20 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>TowerCo Lease Rate (Colocation)</t>
+          <t>Phase 1 TowerCo Co-location Ready (&lt;=1.0 km)</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>120000</v>
+        <v>651</v>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>PHP/site/mo</t>
+          <t>sites</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>Full turnkey macro colocation lease</t>
+          <t>Audited existing towers &lt;=1 km (65.1% of Phase 1)</t>
         </is>
       </c>
     </row>
@@ -1311,20 +1311,145 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
+          <t>Phase 1 Greenfield Own-Build (&gt;2.0 km)</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="n">
+        <v>266</v>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>sites</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>Remote sites requiring new monopole build (26.6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Tower Infrastructure</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Total Program Empirical Co-location Rate</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="n">
+        <v>0.5522</v>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>Empirical ratio of sites with tower &lt;=1.0 km across Combined Hybrid Dual Optimization</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Tower Infrastructure</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Total Program Greenfield Own-Build Rate</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>Empirical ratio of sites with tower &gt;2.0 km across Combined Hybrid Dual Optimization</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Tower Infrastructure</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>TowerCo Lease Rate (Colocation)</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="n">
+        <v>120000</v>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>PHP/site/mo</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>Full turnkey macro colocation lease</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Tower Infrastructure</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
           <t>Own-Site Monopole Build CAPEX</t>
         </is>
       </c>
-      <c r="C33" s="11" t="n">
+      <c r="C37" s="11" t="n">
         <v>3500000</v>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>PHP / site</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>30m monopole, civil shelter, compound</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Tower Infrastructure</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Own-Site Ground Land Lease OPEX</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>PHP/site/mo</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>Land rental for own-built greenfield monopole sites</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1464,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="88" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="192" customWidth="1" min="2" max="2"/>
     <col width="54" customWidth="1" min="3" max="3"/>
-    <col width="124" customWidth="1" min="4" max="4"/>
-    <col width="124" customWidth="1" min="5" max="5"/>
-    <col width="124" customWidth="1" min="6" max="6"/>
-    <col width="124" customWidth="1" min="7" max="7"/>
-    <col width="124" customWidth="1" min="8" max="8"/>
-    <col width="114" customWidth="1" min="9" max="9"/>
-    <col width="114" customWidth="1" min="10" max="10"/>
-    <col width="114" customWidth="1" min="11" max="11"/>
-    <col width="114" customWidth="1" min="12" max="12"/>
-    <col width="114" customWidth="1" min="13" max="13"/>
+    <col width="181" customWidth="1" min="4" max="4"/>
+    <col width="181" customWidth="1" min="5" max="5"/>
+    <col width="181" customWidth="1" min="6" max="6"/>
+    <col width="181" customWidth="1" min="7" max="7"/>
+    <col width="181" customWidth="1" min="8" max="8"/>
+    <col width="181" customWidth="1" min="9" max="9"/>
+    <col width="181" customWidth="1" min="10" max="10"/>
+    <col width="181" customWidth="1" min="11" max="11"/>
+    <col width="181" customWidth="1" min="12" max="12"/>
+    <col width="181" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1613,43 +1738,43 @@
         <v/>
       </c>
       <c r="D8" s="17">
-        <f>ROUND(D5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <f>ROUND((D5*'Assumptions &amp; Levers'!$C$34*'Assumptions &amp; Levers'!$C$36*12+D5*'Assumptions &amp; Levers'!$C$35*'Assumptions &amp; Levers'!$C$38*12)/('Assumptions &amp; Levers'!$C$5*1000000), 2)</f>
         <v/>
       </c>
       <c r="E8" s="17">
-        <f>ROUND(E5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <f>ROUND((E5*'Assumptions &amp; Levers'!$C$34*'Assumptions &amp; Levers'!$C$36*12+E5*'Assumptions &amp; Levers'!$C$35*'Assumptions &amp; Levers'!$C$38*12)/('Assumptions &amp; Levers'!$C$5*1000000), 2)</f>
         <v/>
       </c>
       <c r="F8" s="17">
-        <f>ROUND(F5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <f>ROUND((F5*'Assumptions &amp; Levers'!$C$34*'Assumptions &amp; Levers'!$C$36*12+F5*'Assumptions &amp; Levers'!$C$35*'Assumptions &amp; Levers'!$C$38*12)/('Assumptions &amp; Levers'!$C$5*1000000), 2)</f>
         <v/>
       </c>
       <c r="G8" s="17">
-        <f>ROUND(G5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <f>ROUND((G5*'Assumptions &amp; Levers'!$C$34*'Assumptions &amp; Levers'!$C$36*12+G5*'Assumptions &amp; Levers'!$C$35*'Assumptions &amp; Levers'!$C$38*12)/('Assumptions &amp; Levers'!$C$5*1000000), 2)</f>
         <v/>
       </c>
       <c r="H8" s="17">
-        <f>ROUND(H5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <f>ROUND((H5*'Assumptions &amp; Levers'!$C$34*'Assumptions &amp; Levers'!$C$36*12+H5*'Assumptions &amp; Levers'!$C$35*'Assumptions &amp; Levers'!$C$38*12)/('Assumptions &amp; Levers'!$C$5*1000000), 2)</f>
         <v/>
       </c>
       <c r="I8" s="17">
-        <f>ROUND(I5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <f>ROUND((I5*'Assumptions &amp; Levers'!$C$34*'Assumptions &amp; Levers'!$C$36*12+I5*'Assumptions &amp; Levers'!$C$35*'Assumptions &amp; Levers'!$C$38*12)/('Assumptions &amp; Levers'!$C$5*1000000), 2)</f>
         <v/>
       </c>
       <c r="J8" s="17">
-        <f>ROUND(J5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <f>ROUND((J5*'Assumptions &amp; Levers'!$C$34*'Assumptions &amp; Levers'!$C$36*12+J5*'Assumptions &amp; Levers'!$C$35*'Assumptions &amp; Levers'!$C$38*12)/('Assumptions &amp; Levers'!$C$5*1000000), 2)</f>
         <v/>
       </c>
       <c r="K8" s="17">
-        <f>ROUND(K5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <f>ROUND((K5*'Assumptions &amp; Levers'!$C$34*'Assumptions &amp; Levers'!$C$36*12+K5*'Assumptions &amp; Levers'!$C$35*'Assumptions &amp; Levers'!$C$38*12)/('Assumptions &amp; Levers'!$C$5*1000000), 2)</f>
         <v/>
       </c>
       <c r="L8" s="17">
-        <f>ROUND(L5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <f>ROUND((L5*'Assumptions &amp; Levers'!$C$34*'Assumptions &amp; Levers'!$C$36*12+L5*'Assumptions &amp; Levers'!$C$35*'Assumptions &amp; Levers'!$C$38*12)/('Assumptions &amp; Levers'!$C$5*1000000), 2)</f>
         <v/>
       </c>
       <c r="M8" s="17">
-        <f>ROUND(M5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <f>ROUND((M5*'Assumptions &amp; Levers'!$C$34*'Assumptions &amp; Levers'!$C$36*12+M5*'Assumptions &amp; Levers'!$C$35*'Assumptions &amp; Levers'!$C$38*12)/('Assumptions &amp; Levers'!$C$5*1000000), 2)</f>
         <v/>
       </c>
     </row>
@@ -1725,43 +1850,43 @@
         <v/>
       </c>
       <c r="D10" s="17">
-        <f>ROUND(D5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <f>ROUND(D5*(120000/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
         <v/>
       </c>
       <c r="E10" s="17">
-        <f>ROUND(E5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <f>ROUND(E5*(120000/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
         <v/>
       </c>
       <c r="F10" s="17">
-        <f>ROUND(F5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <f>ROUND(F5*(120000/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
         <v/>
       </c>
       <c r="G10" s="17">
-        <f>ROUND(G5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <f>ROUND(G5*(120000/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
         <v/>
       </c>
       <c r="H10" s="17">
-        <f>ROUND(H5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <f>ROUND(H5*(120000/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
         <v/>
       </c>
       <c r="I10" s="17">
-        <f>ROUND(I5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <f>ROUND(I5*(120000/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
         <v/>
       </c>
       <c r="J10" s="17">
-        <f>ROUND(J5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <f>ROUND(J5*(120000/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
         <v/>
       </c>
       <c r="K10" s="17">
-        <f>ROUND(K5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <f>ROUND(K5*(120000/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
         <v/>
       </c>
       <c r="L10" s="17">
-        <f>ROUND(L5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <f>ROUND(L5*(120000/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
         <v/>
       </c>
       <c r="M10" s="17">
-        <f>ROUND(M5*('Assumptions &amp; Levers'!$C$32/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
+        <f>ROUND(M5*(120000/'Assumptions &amp; Levers'!$C$5)*12/1000000, 2)</f>
         <v/>
       </c>
     </row>
@@ -1931,7 +2056,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Audited Transmission CAPEX ($M)</t>
+          <t>Own-Site Monopole Build CAPEX ($M)</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -1944,23 +2069,23 @@
         <v/>
       </c>
       <c r="D14" s="17">
-        <f>ROUND('Assumptions &amp; Levers'!$C$11*(0.6564*'Assumptions &amp; Levers'!$C$25+0.3436*'Assumptions &amp; Levers'!$C$27)/1000000, 2)</f>
+        <f>ROUND('Assumptions &amp; Levers'!$C$10*'Assumptions &amp; Levers'!$C$35*'Assumptions &amp; Levers'!$C$37/('Assumptions &amp; Levers'!$C$5*1000000), 2)</f>
         <v/>
       </c>
       <c r="E14" s="17">
-        <f>ROUND('Assumptions &amp; Levers'!$C$11*(0.6564*'Assumptions &amp; Levers'!$C$25+0.3436*'Assumptions &amp; Levers'!$C$27)/1000000, 2)</f>
+        <f>ROUND('Assumptions &amp; Levers'!$C$11*'Assumptions &amp; Levers'!$C$35*'Assumptions &amp; Levers'!$C$37/('Assumptions &amp; Levers'!$C$5*1000000), 2)</f>
         <v/>
       </c>
       <c r="F14" s="17">
-        <f>ROUND('Assumptions &amp; Levers'!$C$11*(0.6564*'Assumptions &amp; Levers'!$C$25+0.3436*'Assumptions &amp; Levers'!$C$27)/1000000, 2)</f>
+        <f>ROUND('Assumptions &amp; Levers'!$C$11*'Assumptions &amp; Levers'!$C$35*'Assumptions &amp; Levers'!$C$37/('Assumptions &amp; Levers'!$C$5*1000000), 2)</f>
         <v/>
       </c>
       <c r="G14" s="17">
-        <f>ROUND('Assumptions &amp; Levers'!$C$11*(0.6564*'Assumptions &amp; Levers'!$C$25+0.3436*'Assumptions &amp; Levers'!$C$27)/1000000, 2)</f>
+        <f>ROUND('Assumptions &amp; Levers'!$C$11*'Assumptions &amp; Levers'!$C$35*'Assumptions &amp; Levers'!$C$37/('Assumptions &amp; Levers'!$C$5*1000000), 2)</f>
         <v/>
       </c>
       <c r="H14" s="17">
-        <f>ROUND('Assumptions &amp; Levers'!$C$11*(0.6564*'Assumptions &amp; Levers'!$C$25+0.3436*'Assumptions &amp; Levers'!$C$27)/1000000, 2)</f>
+        <f>ROUND('Assumptions &amp; Levers'!$C$11*'Assumptions &amp; Levers'!$C$35*'Assumptions &amp; Levers'!$C$37/('Assumptions &amp; Levers'!$C$5*1000000), 2)</f>
         <v/>
       </c>
       <c r="I14" s="17" t="n">
@@ -1982,7 +2107,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>CPE Device CAPEX ($M)</t>
+          <t>Audited Transmission CAPEX ($M)</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -1995,50 +2120,45 @@
         <v/>
       </c>
       <c r="D15" s="17">
-        <f>ROUND(D6*'Assumptions &amp; Levers'!$C$23/1000000, 2)</f>
+        <f>ROUND('Assumptions &amp; Levers'!$C$11*(0.6564*'Assumptions &amp; Levers'!$C$25+0.3436*'Assumptions &amp; Levers'!$C$27)/1000000, 2)</f>
         <v/>
       </c>
       <c r="E15" s="17">
-        <f>ROUND((E6-D6)*'Assumptions &amp; Levers'!$C$23/1000000, 2)</f>
+        <f>ROUND('Assumptions &amp; Levers'!$C$11*(0.6564*'Assumptions &amp; Levers'!$C$25+0.3436*'Assumptions &amp; Levers'!$C$27)/1000000, 2)</f>
         <v/>
       </c>
       <c r="F15" s="17">
-        <f>ROUND((F6-E6)*'Assumptions &amp; Levers'!$C$23/1000000, 2)</f>
+        <f>ROUND('Assumptions &amp; Levers'!$C$11*(0.6564*'Assumptions &amp; Levers'!$C$25+0.3436*'Assumptions &amp; Levers'!$C$27)/1000000, 2)</f>
         <v/>
       </c>
       <c r="G15" s="17">
-        <f>ROUND((G6-F6)*'Assumptions &amp; Levers'!$C$23/1000000, 2)</f>
+        <f>ROUND('Assumptions &amp; Levers'!$C$11*(0.6564*'Assumptions &amp; Levers'!$C$25+0.3436*'Assumptions &amp; Levers'!$C$27)/1000000, 2)</f>
         <v/>
       </c>
       <c r="H15" s="17">
-        <f>ROUND((H6-G6)*'Assumptions &amp; Levers'!$C$23/1000000, 2)</f>
-        <v/>
-      </c>
-      <c r="I15" s="17">
-        <f>ROUND((I6-H6)*'Assumptions &amp; Levers'!$C$23/1000000, 2)</f>
-        <v/>
-      </c>
-      <c r="J15" s="17">
-        <f>ROUND((J6-I6)*'Assumptions &amp; Levers'!$C$23/1000000, 2)</f>
-        <v/>
-      </c>
-      <c r="K15" s="17">
-        <f>ROUND((K6-J6)*'Assumptions &amp; Levers'!$C$23/1000000, 2)</f>
-        <v/>
-      </c>
-      <c r="L15" s="17">
-        <f>ROUND((L6-K6)*'Assumptions &amp; Levers'!$C$23/1000000, 2)</f>
-        <v/>
-      </c>
-      <c r="M15" s="17">
-        <f>ROUND((M6-L6)*'Assumptions &amp; Levers'!$C$23/1000000, 2)</f>
-        <v/>
+        <f>ROUND('Assumptions &amp; Levers'!$C$11*(0.6564*'Assumptions &amp; Levers'!$C$25+0.3436*'Assumptions &amp; Levers'!$C$27)/1000000, 2)</f>
+        <v/>
+      </c>
+      <c r="I15" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Total Capital Expenditure ($M)</t>
+          <t>CPE Device CAPEX ($M)</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -2051,226 +2171,281 @@
         <v/>
       </c>
       <c r="D16" s="17">
-        <f>SUM(D13:D15)</f>
+        <f>ROUND(D6*'Assumptions &amp; Levers'!$C$23/1000000, 2)</f>
         <v/>
       </c>
       <c r="E16" s="17">
-        <f>SUM(E13:E15)</f>
+        <f>ROUND((E6-D6)*'Assumptions &amp; Levers'!$C$23/1000000, 2)</f>
         <v/>
       </c>
       <c r="F16" s="17">
-        <f>SUM(F13:F15)</f>
+        <f>ROUND((F6-E6)*'Assumptions &amp; Levers'!$C$23/1000000, 2)</f>
         <v/>
       </c>
       <c r="G16" s="17">
-        <f>SUM(G13:G15)</f>
+        <f>ROUND((G6-F6)*'Assumptions &amp; Levers'!$C$23/1000000, 2)</f>
         <v/>
       </c>
       <c r="H16" s="17">
-        <f>SUM(H13:H15)</f>
+        <f>ROUND((H6-G6)*'Assumptions &amp; Levers'!$C$23/1000000, 2)</f>
         <v/>
       </c>
       <c r="I16" s="17">
-        <f>SUM(I13:I15)</f>
+        <f>ROUND((I6-H6)*'Assumptions &amp; Levers'!$C$23/1000000, 2)</f>
         <v/>
       </c>
       <c r="J16" s="17">
-        <f>SUM(J13:J15)</f>
+        <f>ROUND((J6-I6)*'Assumptions &amp; Levers'!$C$23/1000000, 2)</f>
         <v/>
       </c>
       <c r="K16" s="17">
-        <f>SUM(K13:K15)</f>
+        <f>ROUND((K6-J6)*'Assumptions &amp; Levers'!$C$23/1000000, 2)</f>
         <v/>
       </c>
       <c r="L16" s="17">
-        <f>SUM(L13:L15)</f>
+        <f>ROUND((L6-K6)*'Assumptions &amp; Levers'!$C$23/1000000, 2)</f>
         <v/>
       </c>
       <c r="M16" s="17">
-        <f>SUM(M13:M15)</f>
+        <f>ROUND((M6-L6)*'Assumptions &amp; Levers'!$C$23/1000000, 2)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>Free Cash Flow ($M)</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
-        <is>
-          <t>Cash Flow</t>
-        </is>
-      </c>
-      <c r="C17" s="21">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Total Capital Expenditure ($M)</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="C17" s="16">
         <f>SUM(D17:M17)</f>
         <v/>
       </c>
-      <c r="D17" s="22">
-        <f>D12-D16</f>
-        <v/>
-      </c>
-      <c r="E17" s="22">
-        <f>E12-E16</f>
-        <v/>
-      </c>
-      <c r="F17" s="22">
-        <f>F12-F16</f>
-        <v/>
-      </c>
-      <c r="G17" s="22">
-        <f>G12-G16</f>
-        <v/>
-      </c>
-      <c r="H17" s="22">
-        <f>H12-H16</f>
-        <v/>
-      </c>
-      <c r="I17" s="22">
-        <f>I12-I16</f>
-        <v/>
-      </c>
-      <c r="J17" s="22">
-        <f>J12-J16</f>
-        <v/>
-      </c>
-      <c r="K17" s="22">
-        <f>K12-K16</f>
-        <v/>
-      </c>
-      <c r="L17" s="22">
-        <f>L12-L16</f>
-        <v/>
-      </c>
-      <c r="M17" s="22">
-        <f>M12-M16</f>
+      <c r="D17" s="17">
+        <f>SUM(D13:D16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="17">
+        <f>SUM(E13:E16)</f>
+        <v/>
+      </c>
+      <c r="F17" s="17">
+        <f>SUM(F13:F16)</f>
+        <v/>
+      </c>
+      <c r="G17" s="17">
+        <f>SUM(G13:G16)</f>
+        <v/>
+      </c>
+      <c r="H17" s="17">
+        <f>SUM(H13:H16)</f>
+        <v/>
+      </c>
+      <c r="I17" s="17">
+        <f>SUM(I13:I16)</f>
+        <v/>
+      </c>
+      <c r="J17" s="17">
+        <f>SUM(J13:J16)</f>
+        <v/>
+      </c>
+      <c r="K17" s="17">
+        <f>SUM(K13:K16)</f>
+        <v/>
+      </c>
+      <c r="L17" s="17">
+        <f>SUM(L13:L16)</f>
+        <v/>
+      </c>
+      <c r="M17" s="17">
+        <f>SUM(M13:M16)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="19" t="inlineStr">
         <is>
+          <t>Free Cash Flow ($M)</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>Cash Flow</t>
+        </is>
+      </c>
+      <c r="C18" s="21">
+        <f>SUM(D18:M18)</f>
+        <v/>
+      </c>
+      <c r="D18" s="22">
+        <f>D12-D17</f>
+        <v/>
+      </c>
+      <c r="E18" s="22">
+        <f>E12-E17</f>
+        <v/>
+      </c>
+      <c r="F18" s="22">
+        <f>F12-F17</f>
+        <v/>
+      </c>
+      <c r="G18" s="22">
+        <f>G12-G17</f>
+        <v/>
+      </c>
+      <c r="H18" s="22">
+        <f>H12-H17</f>
+        <v/>
+      </c>
+      <c r="I18" s="22">
+        <f>I12-I17</f>
+        <v/>
+      </c>
+      <c r="J18" s="22">
+        <f>J12-J17</f>
+        <v/>
+      </c>
+      <c r="K18" s="22">
+        <f>K12-K17</f>
+        <v/>
+      </c>
+      <c r="L18" s="22">
+        <f>L12-L17</f>
+        <v/>
+      </c>
+      <c r="M18" s="22">
+        <f>M12-M17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
           <t>Cumulative Free Cash Flow ($M)</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>Cash Flow</t>
         </is>
       </c>
-      <c r="C18" s="21">
+      <c r="C19" s="21">
         <f>M18</f>
         <v/>
       </c>
-      <c r="D18" s="22">
-        <f>D17</f>
-        <v/>
-      </c>
-      <c r="E18" s="22">
-        <f>D18+E17</f>
-        <v/>
-      </c>
-      <c r="F18" s="22">
-        <f>E18+F17</f>
-        <v/>
-      </c>
-      <c r="G18" s="22">
-        <f>F18+G17</f>
-        <v/>
-      </c>
-      <c r="H18" s="22">
-        <f>G18+H17</f>
-        <v/>
-      </c>
-      <c r="I18" s="22">
-        <f>H18+I17</f>
-        <v/>
-      </c>
-      <c r="J18" s="22">
-        <f>I18+J17</f>
-        <v/>
-      </c>
-      <c r="K18" s="22">
-        <f>J18+K17</f>
-        <v/>
-      </c>
-      <c r="L18" s="22">
-        <f>K18+L17</f>
-        <v/>
-      </c>
-      <c r="M18" s="22">
-        <f>L18+M17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="23" t="inlineStr">
+      <c r="D19" s="22">
+        <f>D18</f>
+        <v/>
+      </c>
+      <c r="E19" s="22">
+        <f>D19+E18</f>
+        <v/>
+      </c>
+      <c r="F19" s="22">
+        <f>E19+F18</f>
+        <v/>
+      </c>
+      <c r="G19" s="22">
+        <f>F19+G18</f>
+        <v/>
+      </c>
+      <c r="H19" s="22">
+        <f>G19+H18</f>
+        <v/>
+      </c>
+      <c r="I19" s="22">
+        <f>H19+I18</f>
+        <v/>
+      </c>
+      <c r="J19" s="22">
+        <f>I19+J18</f>
+        <v/>
+      </c>
+      <c r="K19" s="22">
+        <f>J19+K18</f>
+        <v/>
+      </c>
+      <c r="L19" s="22">
+        <f>K19+L18</f>
+        <v/>
+      </c>
+      <c r="M19" s="22">
+        <f>L19+M18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="23" t="inlineStr">
         <is>
           <t>EXECUTIVE VALUATION &amp; RETURN METRICS</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Project 10-Yr NPV (@ 12% WACC)</t>
-        </is>
-      </c>
-      <c r="B21" s="24">
-        <f>NPV('Assumptions &amp; Levers'!$C$6, D17:M17)</f>
-        <v/>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>Discounted cumulative cash return</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Unlevered Project IRR (%)</t>
-        </is>
-      </c>
-      <c r="B22" s="9">
-        <f>IRR(D17:M17)</f>
+          <t>Project 10-Yr NPV (@ 12% WACC)</t>
+        </is>
+      </c>
+      <c r="B22" s="24">
+        <f>NPV('Assumptions &amp; Levers'!$C$6, D18:M18)</f>
         <v/>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Internal rate of return across 10 years</t>
+          <t>Discounted cumulative cash return</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Simple Payback Period</t>
-        </is>
-      </c>
-      <c r="B23" s="25" t="inlineStr">
-        <is>
-          <t>8.3 Years</t>
-        </is>
+          <t>Unlevered Project IRR (%)</t>
+        </is>
+      </c>
+      <c r="B23" s="9">
+        <f>IRR(D18:M18)</f>
+        <v/>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Time to recover cumulative initial capital</t>
+          <t>Internal rate of return across 10 years</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
+          <t>Simple Payback Period</t>
+        </is>
+      </c>
+      <c r="B24" s="25">
+        <f>IF(M19&lt;0, "No Payback (&gt;10 Yrs)", TEXT(ROUND(COUNTIF(D19:M19, "&lt;0") + ABS(INDEX(D19:M19, 1, COUNTIF(D19:M19, "&lt;0"))) / INDEX(D18:M18, 1, COUNTIF(D19:M19, "&lt;0") + 1), 1), "0.0") &amp; " Years")</f>
+        <v/>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Time to recover cumulative initial capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
           <t>Peak Capital Funding Required</t>
         </is>
       </c>
-      <c r="B24" s="24">
-        <f>ABS(MIN(0, MIN(D18:M18)))</f>
-        <v/>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="B25" s="24">
+        <f>ABS(MIN(0, MIN(D19:M19)))</f>
+        <v/>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>Maximum cumulative cash deficit before self-funding</t>
         </is>
